--- a/out/Attention-MambaAMT_repeat_4_000008.xlsx
+++ b/out/Attention-MambaAMT_repeat_4_000008.xlsx
@@ -2527,14 +2527,14 @@
       </c>
       <c r="IZ2" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB2" t="n">
-        <v>-1.829132276861947</v>
+        <v>2.499999930000002</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3322,14 +3322,14 @@
       </c>
       <c r="IZ3" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB3" t="n">
-        <v>0.9817726438401608</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
         <v>1</v>
       </c>
       <c r="JB4" t="n">
-        <v>1.581772643840161</v>
+        <v>3.099999930000001</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>1</v>
       </c>
       <c r="JB5" t="n">
-        <v>1.581772643840161</v>
+        <v>3.099999930000001</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5711,10 +5711,10 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB6" t="n">
-        <v>-1.229132276861947</v>
+        <v>3.099999930000001</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>-1.829132276861947</v>
+        <v>-0.3999999825000004</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>-1.829132276861947</v>
+        <v>-0.3999999825000004</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8096,10 +8096,10 @@
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>0.9817726438401608</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>0</v>
       </c>
       <c r="JB10" t="n">
-        <v>-1.829132276861947</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9686,10 +9686,10 @@
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>1.581772643840161</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10481,10 +10481,10 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>1.581772643840161</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11276,10 +11276,10 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>1.581772643840161</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12071,10 +12071,10 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB14" t="n">
-        <v>1.581772643840161</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12866,10 +12866,10 @@
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>1.581772643840161</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>0</v>
       </c>
       <c r="JB16" t="n">
-        <v>-1.229132276861947</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>-1.829132276861947</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15251,10 +15251,10 @@
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB18" t="n">
-        <v>0.9817726438401608</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16046,10 +16046,10 @@
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB19" t="n">
-        <v>0.9817726438401608</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16841,10 +16841,10 @@
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB20" t="n">
-        <v>1.581772643840161</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17636,10 +17636,10 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB21" t="n">
-        <v>1.581772643840161</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18431,10 +18431,10 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>1.581772643840161</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19226,10 +19226,10 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB23" t="n">
-        <v>1.581772643840161</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20021,10 +20021,10 @@
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>1.581772643840161</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20816,10 +20816,10 @@
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB25" t="n">
-        <v>1.581772643840161</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21611,10 +21611,10 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>1.581772643840161</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22406,10 +22406,10 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB27" t="n">
-        <v>0.9817726438401608</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23201,10 +23201,10 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB28" t="n">
-        <v>0.9817726438401608</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23996,10 +23996,10 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB29" t="n">
-        <v>0.9817726438401608</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24791,10 +24791,10 @@
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB30" t="n">
-        <v>0.9817726438401608</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25586,10 +25586,10 @@
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB31" t="n">
-        <v>0.9817726438401608</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26381,10 +26381,10 @@
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB32" t="n">
-        <v>0.9817726438401608</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>-1.829132276861947</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27971,10 +27971,10 @@
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB34" t="n">
-        <v>0.9817726438401608</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28766,10 +28766,10 @@
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB35" t="n">
-        <v>0.9817726438401608</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29561,10 +29561,10 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB36" t="n">
-        <v>1.581772643840161</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30356,10 +30356,10 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB37" t="n">
-        <v>1.581772643840161</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31151,10 +31151,10 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB38" t="n">
-        <v>1.581772643840161</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31946,10 +31946,10 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB39" t="n">
-        <v>1.581772643840161</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32741,10 +32741,10 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB40" t="n">
-        <v>1.581772643840161</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33539,7 +33539,7 @@
         <v>0</v>
       </c>
       <c r="JB41" t="n">
-        <v>-1.829132276861947</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34331,10 +34331,10 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB42" t="n">
-        <v>0.9817726438401608</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35126,10 +35126,10 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB43" t="n">
-        <v>0.9817726438401608</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35924,7 +35924,7 @@
         <v>1</v>
       </c>
       <c r="JB44" t="n">
-        <v>1.581772643840161</v>
+        <v>3.099999930000001</v>
       </c>
       <c r="JC44" t="n">
         <v>0</v>
@@ -36719,10 +36719,10 @@
         <v>1</v>
       </c>
       <c r="JB45" t="n">
-        <v>1.581772643840161</v>
+        <v>3.099999930000001</v>
       </c>
       <c r="JC45" t="n">
-        <v>-0.0001360795139268739</v>
+        <v>-0.0001707095139203593</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>-0.1563292250221626</v>
+        <v>-0.1961124437100503</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37511,13 +37511,13 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB46" t="n">
-        <v>-1.829132276861947</v>
+        <v>3.099999930000001</v>
       </c>
       <c r="JC46" t="n">
-        <v>-0.1564653045360895</v>
+        <v>-0.1962831532239707</v>
       </c>
     </row>
     <row r="47">
@@ -38309,10 +38309,10 @@
         <v>1</v>
       </c>
       <c r="JB47" t="n">
-        <v>0.9817726438401608</v>
+        <v>3.099999930000001</v>
       </c>
       <c r="JC47" t="n">
-        <v>-0.1564653045360895</v>
+        <v>-0.1962831532239707</v>
       </c>
     </row>
     <row r="48">
@@ -39101,13 +39101,13 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB48" t="n">
-        <v>-1.829132276861947</v>
+        <v>3.099999930000001</v>
       </c>
       <c r="JC48" t="n">
-        <v>-0.1564653045360895</v>
+        <v>-0.1962831532239707</v>
       </c>
     </row>
     <row r="49">
@@ -39896,13 +39896,13 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB49" t="n">
-        <v>-1.829132276861947</v>
+        <v>3.099999930000001</v>
       </c>
       <c r="JC49" t="n">
-        <v>-0.1564653045360895</v>
+        <v>-0.1962831532239707</v>
       </c>
     </row>
     <row r="50">
@@ -40691,13 +40691,13 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB50" t="n">
-        <v>-1.829132276861947</v>
+        <v>3.099999930000001</v>
       </c>
       <c r="JC50" t="n">
-        <v>-0.1564653045360895</v>
+        <v>-0.1962831532239707</v>
       </c>
     </row>
     <row r="51">
@@ -41489,10 +41489,10 @@
         <v>0</v>
       </c>
       <c r="JB51" t="n">
-        <v>-1.829132276861947</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC51" t="n">
-        <v>-0.1564653045360895</v>
+        <v>-0.1962831532239707</v>
       </c>
     </row>
     <row r="52">
@@ -42284,10 +42284,10 @@
         <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>-1.829132276861947</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC52" t="n">
-        <v>-0.1564653045360895</v>
+        <v>-0.1962831532239707</v>
       </c>
     </row>
     <row r="53">
@@ -43079,10 +43079,10 @@
         <v>0</v>
       </c>
       <c r="JB53" t="n">
-        <v>-1.829132276861947</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC53" t="n">
-        <v>-0.1564653045360895</v>
+        <v>-0.1962831532239707</v>
       </c>
     </row>
     <row r="54">
@@ -43871,13 +43871,13 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB54" t="n">
-        <v>-1.829132276861947</v>
+        <v>2.499999930000002</v>
       </c>
       <c r="JC54" t="n">
-        <v>-0.1564653045360895</v>
+        <v>-0.1962831532239707</v>
       </c>
     </row>
     <row r="55">
@@ -44669,10 +44669,10 @@
         <v>1</v>
       </c>
       <c r="JB55" t="n">
-        <v>1.581772643840161</v>
+        <v>2.499999930000002</v>
       </c>
       <c r="JC55" t="n">
-        <v>-0.1564653045360895</v>
+        <v>-0.1962831532239707</v>
       </c>
     </row>
     <row r="56">
@@ -45464,10 +45464,10 @@
         <v>1</v>
       </c>
       <c r="JB56" t="n">
-        <v>1.581772643840161</v>
+        <v>3.099999930000001</v>
       </c>
       <c r="JC56" t="n">
-        <v>-0.1564653045360895</v>
+        <v>-0.1962831532239707</v>
       </c>
     </row>
     <row r="57">
@@ -46259,10 +46259,10 @@
         <v>1</v>
       </c>
       <c r="JB57" t="n">
-        <v>1.581772643840161</v>
+        <v>3.099999930000001</v>
       </c>
       <c r="JC57" t="n">
-        <v>-0.1564653045360895</v>
+        <v>-0.1962831532239707</v>
       </c>
     </row>
     <row r="58">
@@ -47054,10 +47054,10 @@
         <v>1</v>
       </c>
       <c r="JB58" t="n">
-        <v>1.581772643840161</v>
+        <v>3.099999930000001</v>
       </c>
       <c r="JC58" t="n">
-        <v>-0.1564653045360895</v>
+        <v>-0.1962831532239707</v>
       </c>
     </row>
     <row r="59">
@@ -47849,10 +47849,10 @@
         <v>1</v>
       </c>
       <c r="JB59" t="n">
-        <v>1.581772643840161</v>
+        <v>3.099999930000001</v>
       </c>
       <c r="JC59" t="n">
-        <v>-0.1565833150768399</v>
+        <v>-0.1964263733532925</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0.4243387719995836</v>
+        <v>0.5149867112556743</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48641,13 +48641,13 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB60" t="n">
-        <v>-1.229132276861947</v>
+        <v>3.099999930000001</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.6929094893822055</v>
+        <v>0.83453635698072</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0.03023408499879792</v>
+        <v>0.03669273163872274</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49439,10 +49439,10 @@
         <v>1</v>
       </c>
       <c r="JB61" t="n">
-        <v>1.581772643840161</v>
+        <v>3.099999930000001</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.3283576870972174</v>
+        <v>0.3921084994752714</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>0.05302015537710103</v>
+        <v>0.06434642098625522</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50231,13 +50231,13 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB62" t="n">
-        <v>0.9817726438401608</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.4041540799757966</v>
+        <v>0.4840966215318732</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0.06441322715251835</v>
+        <v>0.07817361403282098</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51029,10 +51029,10 @@
         <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>-1.829132276861947</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.4799557014927431</v>
+        <v>0.5760910493513758</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>0.01704551880372945</v>
+        <v>0.02068669692840847</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51821,13 +51821,13 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB64" t="n">
-        <v>-1.829132276861947</v>
+        <v>2.499999930000002</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.4495506489423681</v>
+        <v>0.5391910221686111</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>0.009469117267323727</v>
+        <v>0.01149315324021038</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52616,13 +52616,13 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB65" t="n">
-        <v>0.9817726438401608</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.4514278585354944</v>
+        <v>0.5414702995510339</v>
       </c>
     </row>
     <row r="66">
@@ -53403,7 +53403,7 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>0.0198961949881429</v>
+        <v>0.02414601730670688</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
@@ -53411,13 +53411,13 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB66" t="n">
-        <v>0.9817726438401608</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.4817641530565736</v>
+        <v>0.5782861678805272</v>
       </c>
     </row>
     <row r="67">
@@ -54198,7 +54198,7 @@
         <v>0</v>
       </c>
       <c r="IY67" t="n">
-        <v>0.007813691318574394</v>
+        <v>0.009483761846504088</v>
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
@@ -54206,13 +54206,13 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB67" t="n">
-        <v>1.581772643840161</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.4774778522150605</v>
+        <v>0.5730854528855267</v>
       </c>
     </row>
     <row r="68">
@@ -54993,7 +54993,7 @@
         <v>0</v>
       </c>
       <c r="IY68" t="n">
-        <v>0.005563090616339549</v>
+        <v>0.006753295859609155</v>
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
@@ -55004,10 +55004,10 @@
         <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-1.229132276861947</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.4807875988097997</v>
+        <v>0.5771031175168511</v>
       </c>
     </row>
     <row r="69">
@@ -55788,7 +55788,7 @@
         <v>0</v>
       </c>
       <c r="IY69" t="n">
-        <v>0.002186636394936789</v>
+        <v>0.00265510885853852</v>
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
@@ -55796,13 +55796,13 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>1.581772643840161</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.4795930799690892</v>
+        <v>0.575654779532962</v>
       </c>
     </row>
     <row r="70">
@@ -56583,7 +56583,7 @@
         <v>0</v>
       </c>
       <c r="IY70" t="n">
-        <v>0.001238920425776642</v>
+        <v>0.00150404349050227</v>
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
@@ -56594,10 +56594,10 @@
         <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>-1.829132276861947</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.4798831910844887</v>
+        <v>0.5760077500140937</v>
       </c>
     </row>
     <row r="71">
@@ -57378,7 +57378,7 @@
         <v>0</v>
       </c>
       <c r="IY71" t="n">
-        <v>0.0004694451691954156</v>
+        <v>0.0005704409230340436</v>
       </c>
       <c r="IZ71" t="inlineStr">
         <is>
@@ -57389,10 +57389,10 @@
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-1.829132276861947</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.4795806239374676</v>
+        <v>0.5756418393654786</v>
       </c>
     </row>
     <row r="72">
@@ -58173,7 +58173,7 @@
         <v>0</v>
       </c>
       <c r="IY72" t="n">
-        <v>0.0002173940095700668</v>
+        <v>0.0002647353086369622</v>
       </c>
       <c r="IZ72" t="inlineStr">
         <is>
@@ -58184,10 +58184,10 @@
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-1.829132276861947</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.4795456293051974</v>
+        <v>0.5756004597372303</v>
       </c>
     </row>
     <row r="73">
@@ -58968,7 +58968,7 @@
         <v>0</v>
       </c>
       <c r="IY73" t="n">
-        <v>7.653985472975141e-05</v>
+        <v>9.349368591118489e-05</v>
       </c>
       <c r="IZ73" t="inlineStr">
         <is>
@@ -58979,10 +58979,10 @@
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-1.829132276861947</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.4794811284483105</v>
+        <v>0.5755232934271157</v>
       </c>
     </row>
     <row r="74">
@@ -59763,7 +59763,7 @@
         <v>0</v>
       </c>
       <c r="IY74" t="n">
-        <v>1.884928758295011e-05</v>
+        <v>2.409613085119914e-05</v>
       </c>
       <c r="IZ74" t="inlineStr">
         <is>
@@ -59774,10 +59774,10 @@
         <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>-1.829132276861947</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.4794426868371416</v>
+        <v>0.5754775674235032</v>
       </c>
     </row>
     <row r="75">
@@ -60558,7 +60558,7 @@
         <v>0</v>
       </c>
       <c r="IY75" t="n">
-        <v>6.924643791475056e-06</v>
+        <v>9.78655830142907e-06</v>
       </c>
       <c r="IZ75" t="inlineStr">
         <is>
@@ -60569,10 +60569,10 @@
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-1.829132276861947</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.4794376682210905</v>
+        <v>0.5754725443396</v>
       </c>
     </row>
     <row r="76">
@@ -61353,7 +61353,7 @@
         <v>0</v>
       </c>
       <c r="IY76" t="n">
-        <v>1.677971888793091e-06</v>
+        <v>2.705352179376644e-06</v>
       </c>
       <c r="IZ76" t="inlineStr">
         <is>
@@ -61361,13 +61361,13 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>1.581772643840161</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.4794336134282549</v>
+        <v>0.5754686717117431</v>
       </c>
     </row>
     <row r="77">
@@ -62148,7 +62148,7 @@
         <v>0</v>
       </c>
       <c r="IY77" t="n">
-        <v>-8.167273192660964e-07</v>
+        <v>5.776969076452056e-07</v>
       </c>
       <c r="IZ77" t="inlineStr">
         <is>
@@ -62159,10 +62159,10 @@
         <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-1.229132276861947</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.4794309960248361</v>
+        <v>0.5754666035172394</v>
       </c>
     </row>
     <row r="78">
@@ -62943,7 +62943,7 @@
         <v>0</v>
       </c>
       <c r="IY78" t="n">
-        <v>-3.128590021429696e-06</v>
+        <v>-2.504786695239595e-06</v>
       </c>
       <c r="IZ78" t="inlineStr">
         <is>
@@ -62954,10 +62954,10 @@
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-1.229132276861947</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.4794254787828464</v>
+        <v>0.5754610118572312</v>
       </c>
     </row>
     <row r="79">
@@ -63746,13 +63746,13 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB79" t="n">
-        <v>-1.829132276861947</v>
+        <v>3.099999930000001</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.4794191547888385</v>
+        <v>0.5754546878632233</v>
       </c>
     </row>
     <row r="80">
@@ -64544,10 +64544,10 @@
         <v>1</v>
       </c>
       <c r="JB80" t="n">
-        <v>1.581772643840161</v>
+        <v>3.099999930000001</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.4794137870002601</v>
+        <v>0.5754493200746449</v>
       </c>
     </row>
     <row r="81">
@@ -65336,13 +65336,13 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB81" t="n">
-        <v>-1.229132276861947</v>
+        <v>3.099999930000001</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.4794138237487518</v>
+        <v>0.5754493568231366</v>
       </c>
     </row>
     <row r="82">
@@ -66134,10 +66134,10 @@
         <v>1</v>
       </c>
       <c r="JB82" t="n">
-        <v>1.581772643840161</v>
+        <v>3.099999930000001</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.4794139339942273</v>
+        <v>0.5754494670686121</v>
       </c>
     </row>
     <row r="83">
@@ -66926,13 +66926,13 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB83" t="n">
-        <v>-1.229132276861947</v>
+        <v>3.099999930000001</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.4794140074912109</v>
+        <v>0.5754495405655957</v>
       </c>
     </row>
     <row r="84">
@@ -67721,13 +67721,13 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB84" t="n">
-        <v>1.581772643840161</v>
+        <v>-0.3999999825000004</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.4794141912336701</v>
+        <v>0.5754497243080549</v>
       </c>
     </row>
     <row r="85">
@@ -68516,13 +68516,13 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB85" t="n">
-        <v>1.581772643840161</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.4794157346703266</v>
+        <v>0.5754512677447113</v>
       </c>
     </row>
     <row r="86">
@@ -69311,13 +69311,13 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>1.581772643840161</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.4794172046099996</v>
+        <v>0.5754527376843844</v>
       </c>
     </row>
     <row r="87">
@@ -70106,13 +70106,13 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>1.581772643840161</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.4794184540587217</v>
+        <v>0.5754539871331065</v>
       </c>
     </row>
     <row r="88">
@@ -70901,13 +70901,13 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB88" t="n">
-        <v>1.581772643840161</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.479419813752919</v>
+        <v>0.5754553468273037</v>
       </c>
     </row>
     <row r="89">
@@ -71699,10 +71699,10 @@
         <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>-1.829132276861947</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.4794176088434097</v>
+        <v>0.5754531419177945</v>
       </c>
     </row>
     <row r="90">
@@ -72491,13 +72491,13 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>0.9817726438401608</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.4794172046099996</v>
+        <v>0.5754527376843844</v>
       </c>
     </row>
     <row r="91">
@@ -73286,13 +73286,13 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>0.9817726438401608</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.4794163593946877</v>
+        <v>0.5754518924690725</v>
       </c>
     </row>
     <row r="92">
@@ -74084,10 +74084,10 @@
         <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>-1.829132276861947</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.4794169106220649</v>
+        <v>0.5754524436964498</v>
       </c>
     </row>
     <row r="93">
@@ -74879,10 +74879,10 @@
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-1.829132276861947</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.4794165798856386</v>
+        <v>0.5754521129600233</v>
       </c>
     </row>
     <row r="94">
@@ -75671,13 +75671,13 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>0.9817726438401608</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.4794162858977041</v>
+        <v>0.5754518189720889</v>
       </c>
     </row>
     <row r="95">
@@ -76469,10 +76469,10 @@
         <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-1.829132276861947</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.4794163593946877</v>
+        <v>0.5754518924690725</v>
       </c>
     </row>
     <row r="96">
@@ -77261,13 +77261,13 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>1.581772643840161</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.4794159184127857</v>
+        <v>0.5754514514871706</v>
       </c>
     </row>
     <row r="97">
@@ -78059,10 +78059,10 @@
         <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>-1.829132276861947</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.4794158081673102</v>
+        <v>0.5754513412416949</v>
       </c>
     </row>
     <row r="98">
@@ -78851,13 +78851,13 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>1.581772643840161</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.4794157714188185</v>
+        <v>0.5754513044932033</v>
       </c>
     </row>
     <row r="99">
@@ -79649,10 +79649,10 @@
         <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-1.829132276861947</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.4794159184127857</v>
+        <v>0.5754514514871706</v>
       </c>
     </row>
     <row r="100">
@@ -80441,13 +80441,13 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB100" t="n">
-        <v>1.581772643840161</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.4794154406823921</v>
+        <v>0.5754509737567769</v>
       </c>
     </row>
     <row r="101">
@@ -81236,13 +81236,13 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>1.581772643840161</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.4794163961431794</v>
+        <v>0.5754519292175642</v>
       </c>
     </row>
     <row r="102">
@@ -82034,10 +82034,10 @@
         <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>-1.229132276861947</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.4794163593946877</v>
+        <v>0.5754518924690725</v>
       </c>
     </row>
     <row r="103">
@@ -82826,13 +82826,13 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>1.581772643840161</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.4794160286582613</v>
+        <v>0.5754515617326461</v>
       </c>
     </row>
     <row r="104">
@@ -83624,10 +83624,10 @@
         <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>-1.829132276861947</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.4794164696401632</v>
+        <v>0.575452002714548</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-1.829132276861947</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.4794158449158021</v>
+        <v>0.5754513779901869</v>
       </c>
     </row>
     <row r="106">
@@ -85214,10 +85214,10 @@
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-1.829132276861947</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.4794156611733429</v>
+        <v>0.5754511942477277</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-1.829132276861947</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.4794152569399329</v>
+        <v>0.5754507900143178</v>
       </c>
     </row>
     <row r="108">
@@ -86804,10 +86804,10 @@
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-1.829132276861947</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.479414411724621</v>
+        <v>0.5754499447990058</v>
       </c>
     </row>
     <row r="109">
@@ -87599,10 +87599,10 @@
         <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>-1.829132276861947</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.4794143749761293</v>
+        <v>0.5754499080505141</v>
       </c>
     </row>
     <row r="110">
@@ -88394,10 +88394,10 @@
         <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>-1.829132276861947</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.4794145219700965</v>
+        <v>0.5754500550444813</v>
       </c>
     </row>
     <row r="111">
@@ -89189,10 +89189,10 @@
         <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>-1.829132276861947</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.4794144484731129</v>
+        <v>0.5754499815474977</v>
       </c>
     </row>
     <row r="112">
@@ -89981,13 +89981,13 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>1.581772643840161</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.4794145219700965</v>
+        <v>0.5754500550444813</v>
       </c>
     </row>
     <row r="113">
@@ -90779,10 +90779,10 @@
         <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-1.229132276861947</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.4794145587185885</v>
+        <v>0.5754500917929732</v>
       </c>
     </row>
     <row r="114">
@@ -91571,13 +91571,13 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB114" t="n">
-        <v>1.581772643840161</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.4794144484731129</v>
+        <v>0.5754499815474977</v>
       </c>
     </row>
     <row r="115">
@@ -92369,10 +92369,10 @@
         <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>-1.229132276861947</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.4794148894550148</v>
+        <v>0.5754504225293996</v>
       </c>
     </row>
     <row r="116">
@@ -93164,10 +93164,10 @@
         <v>0</v>
       </c>
       <c r="JB116" t="n">
-        <v>-1.229132276861947</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.4794147792095393</v>
+        <v>0.5754503122839241</v>
       </c>
     </row>
     <row r="117">
@@ -93959,10 +93959,10 @@
         <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>-1.829132276861947</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.4794147424610474</v>
+        <v>0.5754502755354322</v>
       </c>
     </row>
     <row r="118">
@@ -94754,10 +94754,10 @@
         <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>-1.829132276861947</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.4794146689640638</v>
+        <v>0.5754502020384485</v>
       </c>
     </row>
     <row r="119">
@@ -95549,10 +95549,10 @@
         <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>-1.829132276861947</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.4794146322155721</v>
+        <v>0.5754501652899568</v>
       </c>
     </row>
     <row r="120">
@@ -96344,10 +96344,10 @@
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-1.829132276861947</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.479414411724621</v>
+        <v>0.5754499447990058</v>
       </c>
     </row>
     <row r="121">
@@ -97139,10 +97139,10 @@
         <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>-1.829132276861947</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.4794143382276373</v>
+        <v>0.5754498713020222</v>
       </c>
     </row>
     <row r="122">
@@ -97934,10 +97934,10 @@
         <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-1.829132276861947</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.4794142647306537</v>
+        <v>0.5754497978050385</v>
       </c>
     </row>
     <row r="123">
@@ -98729,10 +98729,10 @@
         <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>-1.829132276861947</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.4794143014791457</v>
+        <v>0.5754498345535305</v>
       </c>
     </row>
     <row r="124">
@@ -99521,13 +99521,13 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>1.581772643840161</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.4794141912336701</v>
+        <v>0.5754497243080549</v>
       </c>
     </row>
     <row r="125">
@@ -100316,13 +100316,13 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>1.581772643840161</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.4794143014791457</v>
+        <v>0.5754498345535305</v>
       </c>
     </row>
     <row r="126">
@@ -101111,13 +101111,13 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>1.581772643840161</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.4794145954670802</v>
+        <v>0.5754501285414649</v>
       </c>
     </row>
   </sheetData>

--- a/out/Attention-MambaAMT_repeat_4_000008.xlsx
+++ b/out/Attention-MambaAMT_repeat_4_000008.xlsx
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="JB2" t="n">
-        <v>-1.829132276861947</v>
+        <v>-0.1248090170360408</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>1</v>
       </c>
       <c r="JB3" t="n">
-        <v>0.9817726438401608</v>
+        <v>0.1964372596156287</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
         <v>1</v>
       </c>
       <c r="JB4" t="n">
-        <v>1.581772643840161</v>
+        <v>1.038929812918968</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>1</v>
       </c>
       <c r="JB5" t="n">
-        <v>1.581772643840161</v>
+        <v>0.3964372596156287</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>-1.229132276861947</v>
+        <v>-0.2460552936877103</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>-1.829132276861947</v>
+        <v>-1.088547846991049</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>-1.829132276861947</v>
+        <v>-0.4460552936877104</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>1</v>
       </c>
       <c r="JB9" t="n">
-        <v>0.9817726438401608</v>
+        <v>-0.4460552936877104</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>0</v>
       </c>
       <c r="JB10" t="n">
-        <v>-1.829132276861947</v>
+        <v>0.1964372596156285</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>1</v>
       </c>
       <c r="JB11" t="n">
-        <v>1.581772643840161</v>
+        <v>0.3964372596156286</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>1</v>
       </c>
       <c r="JB12" t="n">
-        <v>1.581772643840161</v>
+        <v>1.038929812918968</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>1</v>
       </c>
       <c r="JB13" t="n">
-        <v>1.581772643840161</v>
+        <v>1.038929812918968</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
         <v>1</v>
       </c>
       <c r="JB14" t="n">
-        <v>1.581772643840161</v>
+        <v>1.038929812918968</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>1</v>
       </c>
       <c r="JB15" t="n">
-        <v>1.581772643840161</v>
+        <v>0.3964372596156286</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>0</v>
       </c>
       <c r="JB16" t="n">
-        <v>-1.229132276861947</v>
+        <v>-0.2460552936877104</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>-1.829132276861947</v>
+        <v>-0.4460552936877105</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15254,7 +15254,7 @@
         <v>1</v>
       </c>
       <c r="JB18" t="n">
-        <v>0.9817726438401608</v>
+        <v>0.1964372596156284</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>1</v>
       </c>
       <c r="JB19" t="n">
-        <v>0.9817726438401608</v>
+        <v>0.8389298129189675</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>1</v>
       </c>
       <c r="JB20" t="n">
-        <v>1.581772643840161</v>
+        <v>1.038929812918968</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17639,7 +17639,7 @@
         <v>1</v>
       </c>
       <c r="JB21" t="n">
-        <v>1.581772643840161</v>
+        <v>1.038929812918968</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>1</v>
       </c>
       <c r="JB22" t="n">
-        <v>1.581772643840161</v>
+        <v>1.038929812918968</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>1</v>
       </c>
       <c r="JB23" t="n">
-        <v>1.581772643840161</v>
+        <v>1.038929812918968</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>1</v>
       </c>
       <c r="JB24" t="n">
-        <v>1.581772643840161</v>
+        <v>1.038929812918968</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20819,7 +20819,7 @@
         <v>1</v>
       </c>
       <c r="JB25" t="n">
-        <v>1.581772643840161</v>
+        <v>1.038929812918968</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21614,7 +21614,7 @@
         <v>1</v>
       </c>
       <c r="JB26" t="n">
-        <v>1.581772643840161</v>
+        <v>1.038929812918968</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>1</v>
       </c>
       <c r="JB27" t="n">
-        <v>0.9817726438401608</v>
+        <v>1.038929812918968</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23204,7 +23204,7 @@
         <v>1</v>
       </c>
       <c r="JB28" t="n">
-        <v>0.9817726438401608</v>
+        <v>0.8389298129189675</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
         <v>1</v>
       </c>
       <c r="JB29" t="n">
-        <v>0.9817726438401608</v>
+        <v>0.8389298129189675</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24794,7 +24794,7 @@
         <v>1</v>
       </c>
       <c r="JB30" t="n">
-        <v>0.9817726438401608</v>
+        <v>0.8389298129189675</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25589,7 +25589,7 @@
         <v>1</v>
       </c>
       <c r="JB31" t="n">
-        <v>0.9817726438401608</v>
+        <v>0.8389298129189675</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26384,7 +26384,7 @@
         <v>1</v>
       </c>
       <c r="JB32" t="n">
-        <v>0.9817726438401608</v>
+        <v>0.1964372596156285</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>-1.829132276861947</v>
+        <v>0.1964372596156285</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27974,7 +27974,7 @@
         <v>1</v>
       </c>
       <c r="JB34" t="n">
-        <v>0.9817726438401608</v>
+        <v>0.1964372596156285</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28769,7 +28769,7 @@
         <v>1</v>
       </c>
       <c r="JB35" t="n">
-        <v>0.9817726438401608</v>
+        <v>0.8389298129189675</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29564,7 +29564,7 @@
         <v>1</v>
       </c>
       <c r="JB36" t="n">
-        <v>1.581772643840161</v>
+        <v>0.8389298129189675</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30359,7 +30359,7 @@
         <v>1</v>
       </c>
       <c r="JB37" t="n">
-        <v>1.581772643840161</v>
+        <v>1.038929812918968</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31154,7 +31154,7 @@
         <v>1</v>
       </c>
       <c r="JB38" t="n">
-        <v>1.581772643840161</v>
+        <v>1.038929812918968</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31949,7 +31949,7 @@
         <v>1</v>
       </c>
       <c r="JB39" t="n">
-        <v>1.581772643840161</v>
+        <v>1.038929812918968</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32744,7 +32744,7 @@
         <v>1</v>
       </c>
       <c r="JB40" t="n">
-        <v>1.581772643840161</v>
+        <v>0.3964372596156286</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33539,7 +33539,7 @@
         <v>0</v>
       </c>
       <c r="JB41" t="n">
-        <v>-1.829132276861947</v>
+        <v>0.1964372596156285</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34334,7 +34334,7 @@
         <v>1</v>
       </c>
       <c r="JB42" t="n">
-        <v>0.9817726438401608</v>
+        <v>0.1964372596156285</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35129,7 +35129,7 @@
         <v>1</v>
       </c>
       <c r="JB43" t="n">
-        <v>0.9817726438401608</v>
+        <v>0.8389298129189675</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35924,7 +35924,7 @@
         <v>1</v>
       </c>
       <c r="JB44" t="n">
-        <v>1.581772643840161</v>
+        <v>0.8389298129189675</v>
       </c>
       <c r="JC44" t="n">
         <v>0</v>
@@ -36719,10 +36719,10 @@
         <v>1</v>
       </c>
       <c r="JB45" t="n">
-        <v>1.581772643840161</v>
+        <v>0.3964372596156286</v>
       </c>
       <c r="JC45" t="n">
-        <v>-0.0001360795139268739</v>
+        <v>-0.0001090425357116619</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>-0.1563292250221626</v>
+        <v>-0.1252689299831935</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37514,10 +37514,10 @@
         <v>0</v>
       </c>
       <c r="JB46" t="n">
-        <v>-1.829132276861947</v>
+        <v>0.1964372596156285</v>
       </c>
       <c r="JC46" t="n">
-        <v>-0.1564653045360895</v>
+        <v>-0.1253779725189052</v>
       </c>
     </row>
     <row r="47">
@@ -38309,10 +38309,10 @@
         <v>1</v>
       </c>
       <c r="JB47" t="n">
-        <v>0.9817726438401608</v>
+        <v>-0.4460552936877105</v>
       </c>
       <c r="JC47" t="n">
-        <v>-0.1564653045360895</v>
+        <v>-0.1253779725189052</v>
       </c>
     </row>
     <row r="48">
@@ -39104,10 +39104,10 @@
         <v>0</v>
       </c>
       <c r="JB48" t="n">
-        <v>-1.829132276861947</v>
+        <v>-0.4460552936877104</v>
       </c>
       <c r="JC48" t="n">
-        <v>-0.1564653045360895</v>
+        <v>-0.1253779725189052</v>
       </c>
     </row>
     <row r="49">
@@ -39899,10 +39899,10 @@
         <v>0</v>
       </c>
       <c r="JB49" t="n">
-        <v>-1.829132276861947</v>
+        <v>-1.088547846991049</v>
       </c>
       <c r="JC49" t="n">
-        <v>-0.1564653045360895</v>
+        <v>-0.1253779725189052</v>
       </c>
     </row>
     <row r="50">
@@ -40694,10 +40694,10 @@
         <v>0</v>
       </c>
       <c r="JB50" t="n">
-        <v>-1.829132276861947</v>
+        <v>-1.088547846991049</v>
       </c>
       <c r="JC50" t="n">
-        <v>-0.1564653045360895</v>
+        <v>-0.1253779725189052</v>
       </c>
     </row>
     <row r="51">
@@ -41489,10 +41489,10 @@
         <v>0</v>
       </c>
       <c r="JB51" t="n">
-        <v>-1.829132276861947</v>
+        <v>-1.088547846991049</v>
       </c>
       <c r="JC51" t="n">
-        <v>-0.1564653045360895</v>
+        <v>-0.1253779725189052</v>
       </c>
     </row>
     <row r="52">
@@ -42284,10 +42284,10 @@
         <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>-1.829132276861947</v>
+        <v>-1.088547846991049</v>
       </c>
       <c r="JC52" t="n">
-        <v>-0.1564653045360895</v>
+        <v>-0.1253779725189052</v>
       </c>
     </row>
     <row r="53">
@@ -43079,10 +43079,10 @@
         <v>0</v>
       </c>
       <c r="JB53" t="n">
-        <v>-1.829132276861947</v>
+        <v>-1.088547846991049</v>
       </c>
       <c r="JC53" t="n">
-        <v>-0.1564653045360895</v>
+        <v>-0.1253779725189052</v>
       </c>
     </row>
     <row r="54">
@@ -43874,10 +43874,10 @@
         <v>0</v>
       </c>
       <c r="JB54" t="n">
-        <v>-1.829132276861947</v>
+        <v>-0.4460552936877104</v>
       </c>
       <c r="JC54" t="n">
-        <v>-0.1564653045360895</v>
+        <v>-0.1253779725189052</v>
       </c>
     </row>
     <row r="55">
@@ -44669,10 +44669,10 @@
         <v>1</v>
       </c>
       <c r="JB55" t="n">
-        <v>1.581772643840161</v>
+        <v>0.3964372596156286</v>
       </c>
       <c r="JC55" t="n">
-        <v>-0.1564653045360895</v>
+        <v>-0.1253779725189052</v>
       </c>
     </row>
     <row r="56">
@@ -45464,10 +45464,10 @@
         <v>1</v>
       </c>
       <c r="JB56" t="n">
-        <v>1.581772643840161</v>
+        <v>1.038929812918968</v>
       </c>
       <c r="JC56" t="n">
-        <v>-0.1564653045360895</v>
+        <v>-0.1253779725189052</v>
       </c>
     </row>
     <row r="57">
@@ -46259,10 +46259,10 @@
         <v>1</v>
       </c>
       <c r="JB57" t="n">
-        <v>1.581772643840161</v>
+        <v>1.038929812918968</v>
       </c>
       <c r="JC57" t="n">
-        <v>-0.1564653045360895</v>
+        <v>-0.1253779725189052</v>
       </c>
     </row>
     <row r="58">
@@ -47054,10 +47054,10 @@
         <v>1</v>
       </c>
       <c r="JB58" t="n">
-        <v>1.581772643840161</v>
+        <v>1.038929812918968</v>
       </c>
       <c r="JC58" t="n">
-        <v>-0.1564653045360895</v>
+        <v>-0.1253779725189052</v>
       </c>
     </row>
     <row r="59">
@@ -47849,10 +47849,10 @@
         <v>1</v>
       </c>
       <c r="JB59" t="n">
-        <v>1.581772643840161</v>
+        <v>0.3964372596156287</v>
       </c>
       <c r="JC59" t="n">
-        <v>-0.1565833150768399</v>
+        <v>-0.1254741810039829</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0.4243387719995836</v>
+        <v>0.345943801760605</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48644,10 +48644,10 @@
         <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>-1.229132276861947</v>
+        <v>0.3964372596156286</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.6929094893822055</v>
+        <v>0.5670776472846354</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0.03023408499879792</v>
+        <v>0.02464838665622772</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49439,10 +49439,10 @@
         <v>1</v>
       </c>
       <c r="JB61" t="n">
-        <v>1.581772643840161</v>
+        <v>0.3964372596156286</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.3283576870972174</v>
+        <v>0.2698757603419139</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>0.05302015537710103</v>
+        <v>0.0432250002889677</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50234,10 +50234,10 @@
         <v>1</v>
       </c>
       <c r="JB62" t="n">
-        <v>0.9817726438401608</v>
+        <v>0.3964372596156286</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.4041540799757966</v>
+        <v>0.3316690753276798</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0.06441322715251835</v>
+        <v>0.05251295873253848</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51029,10 +51029,10 @@
         <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>-1.829132276861947</v>
+        <v>-0.4460552936877104</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.4799557014927431</v>
+        <v>0.3934665037707977</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>0.01704551880372945</v>
+        <v>0.01389640961622947</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51824,10 +51824,10 @@
         <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-1.829132276861947</v>
+        <v>-0.4460552936877102</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.4495506489423681</v>
+        <v>0.3686786947572904</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>0.009469117267323727</v>
+        <v>0.007718768232224536</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52619,10 +52619,10 @@
         <v>1</v>
       </c>
       <c r="JB65" t="n">
-        <v>0.9817726438401608</v>
+        <v>0.1964372596156287</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.4514278585354944</v>
+        <v>0.3702081717512163</v>
       </c>
     </row>
     <row r="66">
@@ -53403,7 +53403,7 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>0.0198961949881429</v>
+        <v>0.01622113109047245</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
@@ -53414,10 +53414,10 @@
         <v>1</v>
       </c>
       <c r="JB66" t="n">
-        <v>0.9817726438401608</v>
+        <v>0.8389298129189675</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.4817641530565736</v>
+        <v>0.3949400330569358</v>
       </c>
     </row>
     <row r="67">
@@ -54198,7 +54198,7 @@
         <v>0</v>
       </c>
       <c r="IY67" t="n">
-        <v>0.007813691318574394</v>
+        <v>0.006368880484767199</v>
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
@@ -54209,10 +54209,10 @@
         <v>1</v>
       </c>
       <c r="JB67" t="n">
-        <v>1.581772643840161</v>
+        <v>0.3964372596156287</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.4774778522150605</v>
+        <v>0.3914448098695998</v>
       </c>
     </row>
     <row r="68">
@@ -54993,7 +54993,7 @@
         <v>0</v>
       </c>
       <c r="IY68" t="n">
-        <v>0.005563090616339549</v>
+        <v>0.004535029275776237</v>
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
@@ -55004,10 +55004,10 @@
         <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-1.229132276861947</v>
+        <v>0.3964372596156286</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.4807875988097997</v>
+        <v>0.3941421205662936</v>
       </c>
     </row>
     <row r="69">
@@ -55788,7 +55788,7 @@
         <v>0</v>
       </c>
       <c r="IY69" t="n">
-        <v>0.002186636394936789</v>
+        <v>0.001781984817680803</v>
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
@@ -55799,10 +55799,10 @@
         <v>1</v>
       </c>
       <c r="JB69" t="n">
-        <v>1.581772643840161</v>
+        <v>-0.4460552936877104</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.4795930799690892</v>
+        <v>0.3931675275153502</v>
       </c>
     </row>
     <row r="70">
@@ -56583,7 +56583,7 @@
         <v>0</v>
       </c>
       <c r="IY70" t="n">
-        <v>0.001238920425776642</v>
+        <v>0.001009249863892231</v>
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
@@ -56594,10 +56594,10 @@
         <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>-1.829132276861947</v>
+        <v>-0.4460552936877104</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.4798831910844887</v>
+        <v>0.3934030011354182</v>
       </c>
     </row>
     <row r="71">
@@ -57378,7 +57378,7 @@
         <v>0</v>
       </c>
       <c r="IY71" t="n">
-        <v>0.0004694451691954156</v>
+        <v>0.0003813674768942865</v>
       </c>
       <c r="IZ71" t="inlineStr">
         <is>
@@ -57389,10 +57389,10 @@
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-1.829132276861947</v>
+        <v>-1.088547846991049</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.4795806239374676</v>
+        <v>0.3931556754142053</v>
       </c>
     </row>
     <row r="72">
@@ -58173,7 +58173,7 @@
         <v>0</v>
       </c>
       <c r="IY72" t="n">
-        <v>0.0002173940095700668</v>
+        <v>0.0001755575127202522</v>
       </c>
       <c r="IZ72" t="inlineStr">
         <is>
@@ -58184,10 +58184,10 @@
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-1.829132276861947</v>
+        <v>-1.088547846991049</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.4795456293051974</v>
+        <v>0.3931262498395371</v>
       </c>
     </row>
     <row r="73">
@@ -58968,7 +58968,7 @@
         <v>0</v>
       </c>
       <c r="IY73" t="n">
-        <v>7.653985472975141e-05</v>
+        <v>6.12006741370259e-05</v>
       </c>
       <c r="IZ73" t="inlineStr">
         <is>
@@ -58979,10 +58979,10 @@
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-1.829132276861947</v>
+        <v>-1.088547846991049</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.4794811284483105</v>
+        <v>0.3930726482252192</v>
       </c>
     </row>
     <row r="74">
@@ -59763,7 +59763,7 @@
         <v>0</v>
       </c>
       <c r="IY74" t="n">
-        <v>1.884928758295011e-05</v>
+        <v>1.455641581801909e-05</v>
       </c>
       <c r="IZ74" t="inlineStr">
         <is>
@@ -59774,10 +59774,10 @@
         <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>-1.829132276861947</v>
+        <v>-1.088547846991049</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.4794426868371416</v>
+        <v>0.393040166571504</v>
       </c>
     </row>
     <row r="75">
@@ -60558,7 +60558,7 @@
         <v>0</v>
       </c>
       <c r="IY75" t="n">
-        <v>6.924643791475056e-06</v>
+        <v>5.016700784839047e-06</v>
       </c>
       <c r="IZ75" t="inlineStr">
         <is>
@@ -60569,10 +60569,10 @@
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-1.829132276861947</v>
+        <v>-0.4460552936877105</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.4794376682210905</v>
+        <v>0.3930351509340212</v>
       </c>
     </row>
     <row r="76">
@@ -61353,7 +61353,7 @@
         <v>0</v>
       </c>
       <c r="IY76" t="n">
-        <v>1.677971888793091e-06</v>
+        <v>1.369014529177619e-07</v>
       </c>
       <c r="IZ76" t="inlineStr">
         <is>
@@ -61364,10 +61364,10 @@
         <v>1</v>
       </c>
       <c r="JB76" t="n">
-        <v>1.581772643840161</v>
+        <v>-0.4460552936877104</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.4794336134282549</v>
+        <v>0.3930309147649473</v>
       </c>
     </row>
     <row r="77">
@@ -62148,7 +62148,7 @@
         <v>0</v>
       </c>
       <c r="IY77" t="n">
-        <v>-8.167273192660964e-07</v>
+        <v>-1.513939432721747e-06</v>
       </c>
       <c r="IZ77" t="inlineStr">
         <is>
@@ -62159,10 +62159,10 @@
         <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-1.229132276861947</v>
+        <v>-0.2460552936877103</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.4794309960248361</v>
+        <v>0.3930279308858416</v>
       </c>
     </row>
     <row r="78">
@@ -62954,10 +62954,10 @@
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-1.229132276861947</v>
+        <v>-0.8885478469910492</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.4794254787828464</v>
+        <v>0.3930224871408353</v>
       </c>
     </row>
     <row r="79">
@@ -63738,7 +63738,7 @@
         <v>0</v>
       </c>
       <c r="IY79" t="n">
-        <v>-4.413072433009741e-06</v>
+        <v>-4.70653621650487e-06</v>
       </c>
       <c r="IZ79" t="inlineStr">
         <is>
@@ -63749,10 +63749,10 @@
         <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-1.829132276861947</v>
+        <v>-0.2460552936877103</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.4794191547888385</v>
+        <v>0.3930164944074049</v>
       </c>
     </row>
     <row r="80">
@@ -64544,10 +64544,10 @@
         <v>1</v>
       </c>
       <c r="JB80" t="n">
-        <v>1.581772643840161</v>
+        <v>-0.2460552936877103</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.4794137870002601</v>
+        <v>0.3930111266188265</v>
       </c>
     </row>
     <row r="81">
@@ -65339,10 +65339,10 @@
         <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>-1.229132276861947</v>
+        <v>0.3964372596156286</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.4794138237487518</v>
+        <v>0.3930111633673182</v>
       </c>
     </row>
     <row r="82">
@@ -66134,10 +66134,10 @@
         <v>1</v>
       </c>
       <c r="JB82" t="n">
-        <v>1.581772643840161</v>
+        <v>-0.2460552936877103</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.4794139339942273</v>
+        <v>0.3930112736127938</v>
       </c>
     </row>
     <row r="83">
@@ -66929,10 +66929,10 @@
         <v>0</v>
       </c>
       <c r="JB83" t="n">
-        <v>-1.229132276861947</v>
+        <v>0.3964372596156286</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.4794140074912109</v>
+        <v>0.3930113471097774</v>
       </c>
     </row>
     <row r="84">
@@ -67724,10 +67724,10 @@
         <v>1</v>
       </c>
       <c r="JB84" t="n">
-        <v>1.581772643840161</v>
+        <v>0.3964372596156286</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.4794141912336701</v>
+        <v>0.3930115308522366</v>
       </c>
     </row>
     <row r="85">
@@ -68519,10 +68519,10 @@
         <v>1</v>
       </c>
       <c r="JB85" t="n">
-        <v>1.581772643840161</v>
+        <v>1.038929812918968</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.4794157346703266</v>
+        <v>0.393013074288893</v>
       </c>
     </row>
     <row r="86">
@@ -69314,10 +69314,10 @@
         <v>1</v>
       </c>
       <c r="JB86" t="n">
-        <v>1.581772643840161</v>
+        <v>1.038929812918968</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.4794172046099996</v>
+        <v>0.3930145442285661</v>
       </c>
     </row>
     <row r="87">
@@ -70109,10 +70109,10 @@
         <v>1</v>
       </c>
       <c r="JB87" t="n">
-        <v>1.581772643840161</v>
+        <v>1.038929812918968</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.4794184540587217</v>
+        <v>0.3930157936772881</v>
       </c>
     </row>
     <row r="88">
@@ -70904,10 +70904,10 @@
         <v>1</v>
       </c>
       <c r="JB88" t="n">
-        <v>1.581772643840161</v>
+        <v>0.3964372596156286</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.479419813752919</v>
+        <v>0.3930171533714854</v>
       </c>
     </row>
     <row r="89">
@@ -71699,10 +71699,10 @@
         <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>-1.829132276861947</v>
+        <v>0.3964372596156285</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.4794176088434097</v>
+        <v>0.3930149484619762</v>
       </c>
     </row>
     <row r="90">
@@ -72494,10 +72494,10 @@
         <v>1</v>
       </c>
       <c r="JB90" t="n">
-        <v>0.9817726438401608</v>
+        <v>0.1964372596156285</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.4794172046099996</v>
+        <v>0.3930145442285661</v>
       </c>
     </row>
     <row r="91">
@@ -73289,10 +73289,10 @@
         <v>1</v>
       </c>
       <c r="JB91" t="n">
-        <v>0.9817726438401608</v>
+        <v>0.1964372596156284</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.4794163593946877</v>
+        <v>0.3930136990132541</v>
       </c>
     </row>
     <row r="92">
@@ -74084,10 +74084,10 @@
         <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>-1.829132276861947</v>
+        <v>-0.4460552936877105</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.4794169106220649</v>
+        <v>0.3930142502406314</v>
       </c>
     </row>
     <row r="93">
@@ -74879,10 +74879,10 @@
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-1.829132276861947</v>
+        <v>-0.4460552936877104</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.4794165798856386</v>
+        <v>0.393013919504205</v>
       </c>
     </row>
     <row r="94">
@@ -75674,10 +75674,10 @@
         <v>1</v>
       </c>
       <c r="JB94" t="n">
-        <v>0.9817726438401608</v>
+        <v>-0.4460552936877105</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.4794162858977041</v>
+        <v>0.3930136255162705</v>
       </c>
     </row>
     <row r="95">
@@ -76469,10 +76469,10 @@
         <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-1.829132276861947</v>
+        <v>0.1964372596156285</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.4794163593946877</v>
+        <v>0.3930136990132541</v>
       </c>
     </row>
     <row r="96">
@@ -77264,10 +77264,10 @@
         <v>1</v>
       </c>
       <c r="JB96" t="n">
-        <v>1.581772643840161</v>
+        <v>-0.4460552936877105</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.4794159184127857</v>
+        <v>0.3930132580313522</v>
       </c>
     </row>
     <row r="97">
@@ -78059,10 +78059,10 @@
         <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>-1.829132276861947</v>
+        <v>0.3964372596156285</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.4794158081673102</v>
+        <v>0.3930131477858766</v>
       </c>
     </row>
     <row r="98">
@@ -78854,10 +78854,10 @@
         <v>1</v>
       </c>
       <c r="JB98" t="n">
-        <v>1.581772643840161</v>
+        <v>-0.4460552936877105</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.4794157714188185</v>
+        <v>0.393013111037385</v>
       </c>
     </row>
     <row r="99">
@@ -79649,10 +79649,10 @@
         <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-1.829132276861947</v>
+        <v>0.3964372596156285</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.4794159184127857</v>
+        <v>0.3930132580313522</v>
       </c>
     </row>
     <row r="100">
@@ -80444,10 +80444,10 @@
         <v>1</v>
       </c>
       <c r="JB100" t="n">
-        <v>1.581772643840161</v>
+        <v>0.3964372596156285</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.4794154406823921</v>
+        <v>0.3930127803009585</v>
       </c>
     </row>
     <row r="101">
@@ -81239,10 +81239,10 @@
         <v>1</v>
       </c>
       <c r="JB101" t="n">
-        <v>1.581772643840161</v>
+        <v>0.3964372596156285</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.4794163961431794</v>
+        <v>0.3930137357617458</v>
       </c>
     </row>
     <row r="102">
@@ -82034,10 +82034,10 @@
         <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>-1.229132276861947</v>
+        <v>0.3964372596156286</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.4794163593946877</v>
+        <v>0.3930136990132541</v>
       </c>
     </row>
     <row r="103">
@@ -82829,10 +82829,10 @@
         <v>1</v>
       </c>
       <c r="JB103" t="n">
-        <v>1.581772643840161</v>
+        <v>-0.2460552936877104</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.4794160286582613</v>
+        <v>0.3930133682768278</v>
       </c>
     </row>
     <row r="104">
@@ -83624,10 +83624,10 @@
         <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>-1.829132276861947</v>
+        <v>-0.4460552936877104</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.4794164696401632</v>
+        <v>0.3930138092587297</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-1.829132276861947</v>
+        <v>-1.088547846991049</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.4794158449158021</v>
+        <v>0.3930131845343686</v>
       </c>
     </row>
     <row r="106">
@@ -85214,10 +85214,10 @@
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-1.829132276861947</v>
+        <v>-1.088547846991049</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.4794156611733429</v>
+        <v>0.3930130007919094</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-1.829132276861947</v>
+        <v>-1.088547846991049</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.4794152569399329</v>
+        <v>0.3930125965584994</v>
       </c>
     </row>
     <row r="108">
@@ -86804,10 +86804,10 @@
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-1.829132276861947</v>
+        <v>-1.088547846991049</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.479414411724621</v>
+        <v>0.3930117513431874</v>
       </c>
     </row>
     <row r="109">
@@ -87599,10 +87599,10 @@
         <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>-1.829132276861947</v>
+        <v>-1.088547846991049</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.4794143749761293</v>
+        <v>0.3930117145946957</v>
       </c>
     </row>
     <row r="110">
@@ -88394,10 +88394,10 @@
         <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>-1.829132276861947</v>
+        <v>-1.088547846991049</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.4794145219700965</v>
+        <v>0.393011861588663</v>
       </c>
     </row>
     <row r="111">
@@ -89189,10 +89189,10 @@
         <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>-1.829132276861947</v>
+        <v>-0.4460552936877105</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.4794144484731129</v>
+        <v>0.3930117880916794</v>
       </c>
     </row>
     <row r="112">
@@ -89984,10 +89984,10 @@
         <v>1</v>
       </c>
       <c r="JB112" t="n">
-        <v>1.581772643840161</v>
+        <v>-0.2460552936877103</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.4794145219700965</v>
+        <v>0.393011861588663</v>
       </c>
     </row>
     <row r="113">
@@ -90779,10 +90779,10 @@
         <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-1.229132276861947</v>
+        <v>0.3964372596156286</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.4794145587185885</v>
+        <v>0.3930118983371549</v>
       </c>
     </row>
     <row r="114">
@@ -91574,10 +91574,10 @@
         <v>1</v>
       </c>
       <c r="JB114" t="n">
-        <v>1.581772643840161</v>
+        <v>-0.2460552936877103</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.4794144484731129</v>
+        <v>0.3930117880916794</v>
       </c>
     </row>
     <row r="115">
@@ -92369,10 +92369,10 @@
         <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>-1.229132276861947</v>
+        <v>-0.2460552936877103</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.4794148894550148</v>
+        <v>0.3930122290735813</v>
       </c>
     </row>
     <row r="116">
@@ -93164,10 +93164,10 @@
         <v>0</v>
       </c>
       <c r="JB116" t="n">
-        <v>-1.229132276861947</v>
+        <v>-0.8885478469910492</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.4794147792095393</v>
+        <v>0.3930121188281057</v>
       </c>
     </row>
     <row r="117">
@@ -93959,10 +93959,10 @@
         <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>-1.829132276861947</v>
+        <v>-1.088547846991049</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.4794147424610474</v>
+        <v>0.3930120820796138</v>
       </c>
     </row>
     <row r="118">
@@ -94754,10 +94754,10 @@
         <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>-1.829132276861947</v>
+        <v>-1.088547846991049</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.4794146689640638</v>
+        <v>0.3930120085826302</v>
       </c>
     </row>
     <row r="119">
@@ -95549,10 +95549,10 @@
         <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>-1.829132276861947</v>
+        <v>-1.088547846991049</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.4794146322155721</v>
+        <v>0.3930119718341385</v>
       </c>
     </row>
     <row r="120">
@@ -96344,10 +96344,10 @@
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-1.829132276861947</v>
+        <v>-1.088547846991049</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.479414411724621</v>
+        <v>0.3930117513431874</v>
       </c>
     </row>
     <row r="121">
@@ -97139,10 +97139,10 @@
         <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>-1.829132276861947</v>
+        <v>-1.088547846991049</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.4794143382276373</v>
+        <v>0.3930116778462038</v>
       </c>
     </row>
     <row r="122">
@@ -97934,10 +97934,10 @@
         <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-1.829132276861947</v>
+        <v>-1.088547846991049</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.4794142647306537</v>
+        <v>0.3930116043492202</v>
       </c>
     </row>
     <row r="123">
@@ -98729,10 +98729,10 @@
         <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>-1.829132276861947</v>
+        <v>-0.2460552936877103</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.4794143014791457</v>
+        <v>0.3930116410977121</v>
       </c>
     </row>
     <row r="124">
@@ -99524,10 +99524,10 @@
         <v>1</v>
       </c>
       <c r="JB124" t="n">
-        <v>1.581772643840161</v>
+        <v>0.3964372596156286</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.4794141912336701</v>
+        <v>0.3930115308522366</v>
       </c>
     </row>
     <row r="125">
@@ -100319,10 +100319,10 @@
         <v>1</v>
       </c>
       <c r="JB125" t="n">
-        <v>1.581772643840161</v>
+        <v>1.038929812918968</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.4794143014791457</v>
+        <v>0.3930116410977121</v>
       </c>
     </row>
     <row r="126">
@@ -101114,10 +101114,10 @@
         <v>1</v>
       </c>
       <c r="JB126" t="n">
-        <v>1.581772643840161</v>
+        <v>1.038929812918968</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.4794145954670802</v>
+        <v>0.3930119350856466</v>
       </c>
     </row>
   </sheetData>

--- a/out/Attention-MambaAMT_repeat_4_000008.xlsx
+++ b/out/Attention-MambaAMT_repeat_4_000008.xlsx
@@ -1731,12 +1731,12 @@
       </c>
       <c r="JA1" s="1" t="inlineStr">
         <is>
-          <t>Predicted Value</t>
+          <t>Original Prediction</t>
         </is>
       </c>
       <c r="JB1" s="1" t="inlineStr">
         <is>
-          <t>Enhanced Signal</t>
+          <t>Trading Signal</t>
         </is>
       </c>
       <c r="JC1" s="1" t="inlineStr">
@@ -2531,10 +2531,10 @@
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>0</v>
+        <v>-0.007303677499294281</v>
       </c>
       <c r="JB2" t="n">
-        <v>-0.1248090170360408</v>
+        <v>-0.1600000000000003</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3322,14 +3322,14 @@
       </c>
       <c r="IZ3" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>1</v>
+        <v>0.005730690434575081</v>
       </c>
       <c r="JB3" t="n">
-        <v>0.1964372596156287</v>
+        <v>-0.1600000000000002</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4121,10 +4121,10 @@
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>1</v>
+        <v>0.06053243577480316</v>
       </c>
       <c r="JB4" t="n">
-        <v>1.038929812918968</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4916,10 +4916,10 @@
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>1</v>
+        <v>0.02841241843998432</v>
       </c>
       <c r="JB5" t="n">
-        <v>0.3964372596156287</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5711,10 +5711,10 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>0</v>
+        <v>-0.01973478868603706</v>
       </c>
       <c r="JB6" t="n">
-        <v>-0.2460552936877103</v>
+        <v>0.16</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6506,10 +6506,10 @@
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>0</v>
+        <v>-0.006819078698754311</v>
       </c>
       <c r="JB7" t="n">
-        <v>-1.088547846991049</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7301,10 +7301,10 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>0</v>
+        <v>-0.001382702961564064</v>
       </c>
       <c r="JB8" t="n">
-        <v>-0.4460552936877104</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8096,10 +8096,10 @@
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>1</v>
+        <v>0.001810947433114052</v>
       </c>
       <c r="JB9" t="n">
-        <v>-0.4460552936877104</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8891,10 +8891,10 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>0</v>
+        <v>-0.0002840626984834671</v>
       </c>
       <c r="JB10" t="n">
-        <v>0.1964372596156285</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9686,10 +9686,10 @@
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>1</v>
+        <v>0.00692804716527462</v>
       </c>
       <c r="JB11" t="n">
-        <v>0.3964372596156286</v>
+        <v>-0.3</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10481,10 +10481,10 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>1</v>
+        <v>0.001972069963812828</v>
       </c>
       <c r="JB12" t="n">
-        <v>1.038929812918968</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11276,10 +11276,10 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>1</v>
+        <v>0.002018259838223457</v>
       </c>
       <c r="JB13" t="n">
-        <v>1.038929812918968</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12071,10 +12071,10 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>1</v>
+        <v>0.006015783175826073</v>
       </c>
       <c r="JB14" t="n">
-        <v>1.038929812918968</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12866,10 +12866,10 @@
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>1</v>
+        <v>0.008656660094857216</v>
       </c>
       <c r="JB15" t="n">
-        <v>0.3964372596156286</v>
+        <v>0.3</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13661,10 +13661,10 @@
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>0</v>
+        <v>-0.01035805232822895</v>
       </c>
       <c r="JB16" t="n">
-        <v>-0.2460552936877104</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14456,10 +14456,10 @@
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>0</v>
+        <v>-0.002604592591524124</v>
       </c>
       <c r="JB17" t="n">
-        <v>-0.4460552936877105</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15251,10 +15251,10 @@
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>1</v>
+        <v>0.00630141980946064</v>
       </c>
       <c r="JB18" t="n">
-        <v>0.1964372596156284</v>
+        <v>0.3</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16046,10 +16046,10 @@
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>1</v>
+        <v>0.008789392188191414</v>
       </c>
       <c r="JB19" t="n">
-        <v>0.8389298129189675</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16841,10 +16841,10 @@
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>1</v>
+        <v>0.008032521232962608</v>
       </c>
       <c r="JB20" t="n">
-        <v>1.038929812918968</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17636,10 +17636,10 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>1</v>
+        <v>0.009477498009800911</v>
       </c>
       <c r="JB21" t="n">
-        <v>1.038929812918968</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18431,10 +18431,10 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>1</v>
+        <v>0.008478725329041481</v>
       </c>
       <c r="JB22" t="n">
-        <v>1.038929812918968</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19226,10 +19226,10 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>1</v>
+        <v>0.01156011410057545</v>
       </c>
       <c r="JB23" t="n">
-        <v>1.038929812918968</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20021,10 +20021,10 @@
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>1</v>
+        <v>0.0128896702080965</v>
       </c>
       <c r="JB24" t="n">
-        <v>1.038929812918968</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20816,10 +20816,10 @@
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>1</v>
+        <v>0.008656533434987068</v>
       </c>
       <c r="JB25" t="n">
-        <v>1.038929812918968</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21611,10 +21611,10 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>1</v>
+        <v>0.006019199267029762</v>
       </c>
       <c r="JB26" t="n">
-        <v>1.038929812918968</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22406,10 +22406,10 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>1</v>
+        <v>0.01186528615653515</v>
       </c>
       <c r="JB27" t="n">
-        <v>1.038929812918968</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23201,10 +23201,10 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>1</v>
+        <v>0.01437407173216343</v>
       </c>
       <c r="JB28" t="n">
-        <v>0.8389298129189675</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23996,10 +23996,10 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>1</v>
+        <v>0.01274817623198032</v>
       </c>
       <c r="JB29" t="n">
-        <v>0.8389298129189675</v>
+        <v>0.2599999999999998</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24791,10 +24791,10 @@
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>1</v>
+        <v>0.01059876568615437</v>
       </c>
       <c r="JB30" t="n">
-        <v>0.8389298129189675</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25586,10 +25586,10 @@
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>1</v>
+        <v>0.008767766878008842</v>
       </c>
       <c r="JB31" t="n">
-        <v>0.8389298129189675</v>
+        <v>-0.16</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26381,10 +26381,10 @@
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>1</v>
+        <v>0.007284721359610558</v>
       </c>
       <c r="JB32" t="n">
-        <v>0.1964372596156285</v>
+        <v>-0.3</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27176,10 +27176,10 @@
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>0</v>
+        <v>-0.002033060416579247</v>
       </c>
       <c r="JB33" t="n">
-        <v>0.1964372596156285</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27971,10 +27971,10 @@
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>1</v>
+        <v>0.002038650214672089</v>
       </c>
       <c r="JB34" t="n">
-        <v>0.1964372596156285</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28766,10 +28766,10 @@
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>1</v>
+        <v>0.005011359229683876</v>
       </c>
       <c r="JB35" t="n">
-        <v>0.8389298129189675</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29561,10 +29561,10 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>1</v>
+        <v>0.002138134092092514</v>
       </c>
       <c r="JB36" t="n">
-        <v>0.8389298129189675</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30356,10 +30356,10 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>1</v>
+        <v>0.002275640144944191</v>
       </c>
       <c r="JB37" t="n">
-        <v>1.038929812918968</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31151,10 +31151,10 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>1</v>
+        <v>0.006232397630810738</v>
       </c>
       <c r="JB38" t="n">
-        <v>1.038929812918968</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31946,10 +31946,10 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>1</v>
+        <v>0.009327711537480354</v>
       </c>
       <c r="JB39" t="n">
-        <v>1.038929812918968</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32741,10 +32741,10 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>1</v>
+        <v>0.005186015740036964</v>
       </c>
       <c r="JB40" t="n">
-        <v>0.3964372596156286</v>
+        <v>0.16</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33536,10 +33536,10 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>0</v>
+        <v>-0.000863153487443924</v>
       </c>
       <c r="JB41" t="n">
-        <v>0.1964372596156285</v>
+        <v>0.3</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34331,10 +34331,10 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>1</v>
+        <v>0.001214323565363884</v>
       </c>
       <c r="JB42" t="n">
-        <v>0.1964372596156285</v>
+        <v>0.3</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35126,10 +35126,10 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>1</v>
+        <v>0.01720107160508633</v>
       </c>
       <c r="JB43" t="n">
-        <v>0.8389298129189675</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35921,10 +35921,10 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>1</v>
+        <v>0.08086469769477844</v>
       </c>
       <c r="JB44" t="n">
-        <v>0.8389298129189675</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC44" t="n">
         <v>0</v>
@@ -36716,13 +36716,13 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>1</v>
+        <v>0.03310433775186539</v>
       </c>
       <c r="JB45" t="n">
-        <v>0.3964372596156286</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC45" t="n">
-        <v>-0.0001090425357116619</v>
+        <v>-0.0001164229180378607</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>-0.1252689299831935</v>
+        <v>-0.1337475717430304</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37511,13 +37511,13 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>0</v>
+        <v>-0.0694696307182312</v>
       </c>
       <c r="JB46" t="n">
-        <v>0.1964372596156285</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC46" t="n">
-        <v>-0.1253779725189052</v>
+        <v>-0.1338639946610683</v>
       </c>
     </row>
     <row r="47">
@@ -38306,13 +38306,13 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>1</v>
+        <v>0.04231128096580505</v>
       </c>
       <c r="JB47" t="n">
-        <v>-0.4460552936877105</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC47" t="n">
-        <v>-0.1253779725189052</v>
+        <v>-0.1338639946610683</v>
       </c>
     </row>
     <row r="48">
@@ -39101,13 +39101,13 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>0</v>
+        <v>-0.03023047745227814</v>
       </c>
       <c r="JB48" t="n">
-        <v>-0.4460552936877104</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC48" t="n">
-        <v>-0.1253779725189052</v>
+        <v>-0.1338639946610683</v>
       </c>
     </row>
     <row r="49">
@@ -39896,13 +39896,13 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>0</v>
+        <v>-0.007358716800808907</v>
       </c>
       <c r="JB49" t="n">
-        <v>-1.088547846991049</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC49" t="n">
-        <v>-0.1253779725189052</v>
+        <v>-0.1338639946610683</v>
       </c>
     </row>
     <row r="50">
@@ -40691,13 +40691,13 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>0</v>
+        <v>-0.01328487135469913</v>
       </c>
       <c r="JB50" t="n">
-        <v>-1.088547846991049</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC50" t="n">
-        <v>-0.1253779725189052</v>
+        <v>-0.1338639946610683</v>
       </c>
     </row>
     <row r="51">
@@ -41486,13 +41486,13 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>0</v>
+        <v>-0.005022799596190453</v>
       </c>
       <c r="JB51" t="n">
-        <v>-1.088547846991049</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC51" t="n">
-        <v>-0.1253779725189052</v>
+        <v>-0.1338639946610683</v>
       </c>
     </row>
     <row r="52">
@@ -42281,13 +42281,13 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>0</v>
+        <v>-0.0066249780356884</v>
       </c>
       <c r="JB52" t="n">
-        <v>-1.088547846991049</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC52" t="n">
-        <v>-0.1253779725189052</v>
+        <v>-0.1338639946610683</v>
       </c>
     </row>
     <row r="53">
@@ -43076,13 +43076,13 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>0</v>
+        <v>-0.0004232265055179596</v>
       </c>
       <c r="JB53" t="n">
-        <v>-1.088547846991049</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC53" t="n">
-        <v>-0.1253779725189052</v>
+        <v>-0.1338639946610683</v>
       </c>
     </row>
     <row r="54">
@@ -43871,13 +43871,13 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>0</v>
+        <v>-0.002274289727210999</v>
       </c>
       <c r="JB54" t="n">
-        <v>-0.4460552936877104</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC54" t="n">
-        <v>-0.1253779725189052</v>
+        <v>-0.1338639946610683</v>
       </c>
     </row>
     <row r="55">
@@ -44666,13 +44666,13 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>1</v>
+        <v>0.0008581113070249557</v>
       </c>
       <c r="JB55" t="n">
-        <v>0.3964372596156286</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC55" t="n">
-        <v>-0.1253779725189052</v>
+        <v>-0.1338639946610683</v>
       </c>
     </row>
     <row r="56">
@@ -45461,13 +45461,13 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>1</v>
+        <v>0.001509329304099083</v>
       </c>
       <c r="JB56" t="n">
-        <v>1.038929812918968</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC56" t="n">
-        <v>-0.1253779725189052</v>
+        <v>-0.1338639946610683</v>
       </c>
     </row>
     <row r="57">
@@ -46256,13 +46256,13 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>1</v>
+        <v>0.004858521744608879</v>
       </c>
       <c r="JB57" t="n">
-        <v>1.038929812918968</v>
+        <v>0.3</v>
       </c>
       <c r="JC57" t="n">
-        <v>-0.1253779725189052</v>
+        <v>-0.1338639946610683</v>
       </c>
     </row>
     <row r="58">
@@ -47051,13 +47051,13 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>1</v>
+        <v>0.02861163951456547</v>
       </c>
       <c r="JB58" t="n">
-        <v>1.038929812918968</v>
+        <v>0.3</v>
       </c>
       <c r="JC58" t="n">
-        <v>-0.1253779725189052</v>
+        <v>-0.1338639946610683</v>
       </c>
     </row>
     <row r="59">
@@ -47846,13 +47846,13 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>1</v>
+        <v>0.0758824422955513</v>
       </c>
       <c r="JB59" t="n">
-        <v>0.3964372596156287</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC59" t="n">
-        <v>-0.1254741810039829</v>
+        <v>-0.1339632802291097</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0.345943801760605</v>
+        <v>0.3570080345747745</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48641,13 +48641,13 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>0</v>
+        <v>-0.04673126712441444</v>
       </c>
       <c r="JB60" t="n">
-        <v>0.3964372596156286</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.5670776472846354</v>
+        <v>0.580738771898895</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0.02464838665622772</v>
+        <v>0.02543674750750171</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49436,13 +49436,13 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>1</v>
+        <v>0.03460797667503357</v>
       </c>
       <c r="JB61" t="n">
-        <v>0.3964372596156286</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.2698757603419139</v>
+        <v>0.274031111284032</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>0.0432250002889677</v>
+        <v>0.04460751661091531</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50231,13 +50231,13 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>1</v>
+        <v>0.05626918375492096</v>
       </c>
       <c r="JB62" t="n">
-        <v>0.3964372596156286</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.3316690753276798</v>
+        <v>0.3378008349680961</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0.05251295873253848</v>
+        <v>0.05419286457635664</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51026,13 +51026,13 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>0</v>
+        <v>-0.04099522531032562</v>
       </c>
       <c r="JB63" t="n">
-        <v>-0.4460552936877104</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.3934665037707977</v>
+        <v>0.4015748030810274</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>0.01389640961622947</v>
+        <v>0.01434062476676132</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51821,13 +51821,13 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>0</v>
+        <v>-0.03147462010383606</v>
       </c>
       <c r="JB64" t="n">
-        <v>-0.4460552936877102</v>
+        <v>-0.3</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.3686786947572904</v>
+        <v>0.3759943284802746</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>0.007718768232224536</v>
+        <v>0.007966040344917233</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52616,13 +52616,13 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>1</v>
+        <v>0.09511320292949677</v>
       </c>
       <c r="JB65" t="n">
-        <v>0.1964372596156287</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.3702081717512163</v>
+        <v>0.3775728929704919</v>
       </c>
     </row>
     <row r="66">
@@ -53403,7 +53403,7 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>0.01622113109047245</v>
+        <v>0.01673887594146502</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
@@ -53411,13 +53411,13 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>1</v>
+        <v>0.01870320923626423</v>
       </c>
       <c r="JB66" t="n">
-        <v>0.8389298129189675</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.3949400330569358</v>
+        <v>0.4030953199304976</v>
       </c>
     </row>
     <row r="67">
@@ -54198,7 +54198,7 @@
         <v>0</v>
       </c>
       <c r="IY67" t="n">
-        <v>0.006368880484767199</v>
+        <v>0.00657355192727635</v>
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
@@ -54206,13 +54206,13 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>1</v>
+        <v>0.03126561641693115</v>
       </c>
       <c r="JB67" t="n">
-        <v>0.3964372596156287</v>
+        <v>-0.16</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.3914448098695998</v>
+        <v>0.3994883636710751</v>
       </c>
     </row>
     <row r="68">
@@ -54993,7 +54993,7 @@
         <v>0</v>
       </c>
       <c r="IY68" t="n">
-        <v>0.004535029275776237</v>
+        <v>0.004679923827130798</v>
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
@@ -55001,13 +55001,13 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>0</v>
+        <v>-0.01885508932173252</v>
       </c>
       <c r="JB68" t="n">
-        <v>0.3964372596156286</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.3941421205662936</v>
+        <v>0.4022719183261736</v>
       </c>
     </row>
     <row r="69">
@@ -55788,7 +55788,7 @@
         <v>0</v>
       </c>
       <c r="IY69" t="n">
-        <v>0.001781984817680803</v>
+        <v>0.001839016248032318</v>
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
@@ -55796,13 +55796,13 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>1</v>
+        <v>0.01826202310621738</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.4460552936877104</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.3931675275153502</v>
+        <v>0.4012663808161579</v>
       </c>
     </row>
     <row r="70">
@@ -56583,7 +56583,7 @@
         <v>0</v>
       </c>
       <c r="IY70" t="n">
-        <v>0.001009249863892231</v>
+        <v>0.00104161954039943</v>
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
@@ -56591,13 +56591,13 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>0</v>
+        <v>-0.02862317860126495</v>
       </c>
       <c r="JB70" t="n">
-        <v>-0.4460552936877104</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.3934030011354182</v>
+        <v>0.4015095291262278</v>
       </c>
     </row>
     <row r="71">
@@ -57378,7 +57378,7 @@
         <v>0</v>
       </c>
       <c r="IY71" t="n">
-        <v>0.0003813674768942865</v>
+        <v>0.0003931111692011037</v>
       </c>
       <c r="IZ71" t="inlineStr">
         <is>
@@ -57386,13 +57386,13 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>0</v>
+        <v>-0.03415615856647491</v>
       </c>
       <c r="JB71" t="n">
-        <v>-1.088547846991049</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.3931556754142053</v>
+        <v>0.4012544703966556</v>
       </c>
     </row>
     <row r="72">
@@ -58173,7 +58173,7 @@
         <v>0</v>
       </c>
       <c r="IY72" t="n">
-        <v>0.0001755575127202522</v>
+        <v>0.0001821632753807493</v>
       </c>
       <c r="IZ72" t="inlineStr">
         <is>
@@ -58181,13 +58181,13 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>0</v>
+        <v>-0.04303190112113953</v>
       </c>
       <c r="JB72" t="n">
-        <v>-1.088547846991049</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.3931262498395371</v>
+        <v>0.4012242273892998</v>
       </c>
     </row>
     <row r="73">
@@ -58968,7 +58968,7 @@
         <v>0</v>
       </c>
       <c r="IY73" t="n">
-        <v>6.12006741370259e-05</v>
+        <v>6.362265002008783e-05</v>
       </c>
       <c r="IZ73" t="inlineStr">
         <is>
@@ -58976,13 +58976,13 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>0</v>
+        <v>-0.0462525337934494</v>
       </c>
       <c r="JB73" t="n">
-        <v>-1.088547846991049</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.3930726482252192</v>
+        <v>0.4011691524107316</v>
       </c>
     </row>
     <row r="74">
@@ -59763,7 +59763,7 @@
         <v>0</v>
       </c>
       <c r="IY74" t="n">
-        <v>1.455641581801909e-05</v>
+        <v>1.503340156967809e-05</v>
       </c>
       <c r="IZ74" t="inlineStr">
         <is>
@@ -59771,13 +59771,13 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>0</v>
+        <v>-0.01796940341591835</v>
       </c>
       <c r="JB74" t="n">
-        <v>-1.088547846991049</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.393040166571504</v>
+        <v>0.4011360085395214</v>
       </c>
     </row>
     <row r="75">
@@ -60566,13 +60566,13 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>0</v>
+        <v>-0.03235432505607605</v>
       </c>
       <c r="JB75" t="n">
-        <v>-0.4460552936877105</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.3930351509340212</v>
+        <v>0.4011309929020386</v>
       </c>
     </row>
     <row r="76">
@@ -61353,7 +61353,7 @@
         <v>0</v>
       </c>
       <c r="IY76" t="n">
-        <v>1.369014529177619e-07</v>
+        <v>6.505915982095382e-07</v>
       </c>
       <c r="IZ76" t="inlineStr">
         <is>
@@ -61361,13 +61361,13 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>1</v>
+        <v>0.0009460411965847015</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.4460552936877104</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.3930309147649473</v>
+        <v>0.4011267926927162</v>
       </c>
     </row>
     <row r="77">
@@ -62156,13 +62156,13 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>0</v>
+        <v>-0.02613397873938084</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.2460552936877103</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.3930279308858416</v>
+        <v>0.4011238088136106</v>
       </c>
     </row>
     <row r="78">
@@ -62951,13 +62951,13 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>0</v>
+        <v>-0.04168552905321121</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.8885478469910492</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.3930224871408353</v>
+        <v>0.4011183650686043</v>
       </c>
     </row>
     <row r="79">
@@ -63746,13 +63746,13 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>0</v>
+        <v>-0.03384993970394135</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.2460552936877103</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.3930164944074049</v>
+        <v>0.4011123723351739</v>
       </c>
     </row>
     <row r="80">
@@ -64541,13 +64541,13 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>1</v>
+        <v>0.008818423375487328</v>
       </c>
       <c r="JB80" t="n">
-        <v>-0.2460552936877103</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.3930111266188265</v>
+        <v>0.4011070045465955</v>
       </c>
     </row>
     <row r="81">
@@ -65336,13 +65336,13 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>0</v>
+        <v>-0.02174351923167706</v>
       </c>
       <c r="JB81" t="n">
-        <v>0.3964372596156286</v>
+        <v>0.16</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.3930111633673182</v>
+        <v>0.4011070412950872</v>
       </c>
     </row>
     <row r="82">
@@ -66131,13 +66131,13 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>1</v>
+        <v>0.00646519847214222</v>
       </c>
       <c r="JB82" t="n">
-        <v>-0.2460552936877103</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.3930112736127938</v>
+        <v>0.4011071515405628</v>
       </c>
     </row>
     <row r="83">
@@ -66926,13 +66926,13 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>0</v>
+        <v>-0.01148405484855175</v>
       </c>
       <c r="JB83" t="n">
-        <v>0.3964372596156286</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.3930113471097774</v>
+        <v>0.4011072250375464</v>
       </c>
     </row>
     <row r="84">
@@ -67721,13 +67721,13 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>1</v>
+        <v>0.06615004688501358</v>
       </c>
       <c r="JB84" t="n">
-        <v>0.3964372596156286</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.3930115308522366</v>
+        <v>0.4011074087800055</v>
       </c>
     </row>
     <row r="85">
@@ -68516,13 +68516,13 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>1</v>
+        <v>0.04143033921718597</v>
       </c>
       <c r="JB85" t="n">
-        <v>1.038929812918968</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.393013074288893</v>
+        <v>0.401108952216662</v>
       </c>
     </row>
     <row r="86">
@@ -69311,13 +69311,13 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>1</v>
+        <v>0.03874102979898453</v>
       </c>
       <c r="JB86" t="n">
-        <v>1.038929812918968</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.3930145442285661</v>
+        <v>0.4011104221563351</v>
       </c>
     </row>
     <row r="87">
@@ -70106,13 +70106,13 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>1</v>
+        <v>0.06846369057893753</v>
       </c>
       <c r="JB87" t="n">
-        <v>1.038929812918968</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.3930157936772881</v>
+        <v>0.4011116716050571</v>
       </c>
     </row>
     <row r="88">
@@ -70901,13 +70901,13 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>1</v>
+        <v>0.03636161983013153</v>
       </c>
       <c r="JB88" t="n">
-        <v>0.3964372596156286</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.3930171533714854</v>
+        <v>0.4011130312992544</v>
       </c>
     </row>
     <row r="89">
@@ -71696,13 +71696,13 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>0</v>
+        <v>-0.02085259556770325</v>
       </c>
       <c r="JB89" t="n">
-        <v>0.3964372596156285</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.3930149484619762</v>
+        <v>0.4011108263897451</v>
       </c>
     </row>
     <row r="90">
@@ -72491,13 +72491,13 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>1</v>
+        <v>0.006983345374464989</v>
       </c>
       <c r="JB90" t="n">
-        <v>0.1964372596156285</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.3930145442285661</v>
+        <v>0.4011104221563351</v>
       </c>
     </row>
     <row r="91">
@@ -73286,13 +73286,13 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>1</v>
+        <v>0.02422738634049892</v>
       </c>
       <c r="JB91" t="n">
-        <v>0.1964372596156284</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.3930136990132541</v>
+        <v>0.4011095769410231</v>
       </c>
     </row>
     <row r="92">
@@ -74081,13 +74081,13 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>0</v>
+        <v>-0.003162549808621407</v>
       </c>
       <c r="JB92" t="n">
-        <v>-0.4460552936877105</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.3930142502406314</v>
+        <v>0.4011101281684004</v>
       </c>
     </row>
     <row r="93">
@@ -74876,13 +74876,13 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>0</v>
+        <v>-0.00112941674888134</v>
       </c>
       <c r="JB93" t="n">
-        <v>-0.4460552936877104</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.393013919504205</v>
+        <v>0.4011097974319739</v>
       </c>
     </row>
     <row r="94">
@@ -75671,13 +75671,13 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>1</v>
+        <v>0.01942749880254269</v>
       </c>
       <c r="JB94" t="n">
-        <v>-0.4460552936877105</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.3930136255162705</v>
+        <v>0.4011095034440395</v>
       </c>
     </row>
     <row r="95">
@@ -76466,13 +76466,13 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>0</v>
+        <v>-0.02021096646785736</v>
       </c>
       <c r="JB95" t="n">
-        <v>0.1964372596156285</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.3930136990132541</v>
+        <v>0.4011095769410231</v>
       </c>
     </row>
     <row r="96">
@@ -77261,13 +77261,13 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>1</v>
+        <v>0.005620328709483147</v>
       </c>
       <c r="JB96" t="n">
-        <v>-0.4460552936877105</v>
+        <v>-0.16</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.3930132580313522</v>
+        <v>0.4011091359591212</v>
       </c>
     </row>
     <row r="97">
@@ -78056,13 +78056,13 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>0</v>
+        <v>-0.003231272101402283</v>
       </c>
       <c r="JB97" t="n">
-        <v>0.3964372596156285</v>
+        <v>0.16</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.3930131477858766</v>
+        <v>0.4011090257136456</v>
       </c>
     </row>
     <row r="98">
@@ -78851,13 +78851,13 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>1</v>
+        <v>0.01697447337210178</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.4460552936877105</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.393013111037385</v>
+        <v>0.4011089889651539</v>
       </c>
     </row>
     <row r="99">
@@ -79646,13 +79646,13 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>0</v>
+        <v>-0.02421567961573601</v>
       </c>
       <c r="JB99" t="n">
-        <v>0.3964372596156285</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.3930132580313522</v>
+        <v>0.4011091359591212</v>
       </c>
     </row>
     <row r="100">
@@ -80441,13 +80441,13 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>1</v>
+        <v>0.06421288847923279</v>
       </c>
       <c r="JB100" t="n">
-        <v>0.3964372596156285</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.3930127803009585</v>
+        <v>0.4011086582287275</v>
       </c>
     </row>
     <row r="101">
@@ -81236,13 +81236,13 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>1</v>
+        <v>0.02967575006186962</v>
       </c>
       <c r="JB101" t="n">
-        <v>0.3964372596156285</v>
+        <v>0.3</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.3930137357617458</v>
+        <v>0.4011096136895148</v>
       </c>
     </row>
     <row r="102">
@@ -82031,13 +82031,13 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>0</v>
+        <v>-0.01963792368769646</v>
       </c>
       <c r="JB102" t="n">
-        <v>0.3964372596156286</v>
+        <v>0.3</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.3930136990132541</v>
+        <v>0.4011095769410231</v>
       </c>
     </row>
     <row r="103">
@@ -82826,13 +82826,13 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>1</v>
+        <v>0.0100873988121748</v>
       </c>
       <c r="JB103" t="n">
-        <v>-0.2460552936877104</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.3930133682768278</v>
+        <v>0.4011092462045967</v>
       </c>
     </row>
     <row r="104">
@@ -83621,13 +83621,13 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>0</v>
+        <v>-0.008016174659132957</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.4460552936877104</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.3930138092587297</v>
+        <v>0.4011096871864986</v>
       </c>
     </row>
     <row r="105">
@@ -84416,13 +84416,13 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>0</v>
+        <v>-0.02173522301018238</v>
       </c>
       <c r="JB105" t="n">
-        <v>-1.088547846991049</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.3930131845343686</v>
+        <v>0.4011090624621376</v>
       </c>
     </row>
     <row r="106">
@@ -85211,13 +85211,13 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>0</v>
+        <v>-0.01877125725150108</v>
       </c>
       <c r="JB106" t="n">
-        <v>-1.088547846991049</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.3930130007919094</v>
+        <v>0.4011088787196784</v>
       </c>
     </row>
     <row r="107">
@@ -86006,13 +86006,13 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>0</v>
+        <v>-0.05683842301368713</v>
       </c>
       <c r="JB107" t="n">
-        <v>-1.088547846991049</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.3930125965584994</v>
+        <v>0.4011084744862684</v>
       </c>
     </row>
     <row r="108">
@@ -86801,13 +86801,13 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>0</v>
+        <v>-0.02925523370504379</v>
       </c>
       <c r="JB108" t="n">
-        <v>-1.088547846991049</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.3930117513431874</v>
+        <v>0.4011076292709564</v>
       </c>
     </row>
     <row r="109">
@@ -87596,13 +87596,13 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>0</v>
+        <v>-0.0005254168063402176</v>
       </c>
       <c r="JB109" t="n">
-        <v>-1.088547846991049</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.3930117145946957</v>
+        <v>0.4011075925224647</v>
       </c>
     </row>
     <row r="110">
@@ -88391,13 +88391,13 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>0</v>
+        <v>-0.04505728557705879</v>
       </c>
       <c r="JB110" t="n">
-        <v>-1.088547846991049</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.393011861588663</v>
+        <v>0.4011077395164319</v>
       </c>
     </row>
     <row r="111">
@@ -89186,13 +89186,13 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>0</v>
+        <v>-0.01102313585579395</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.4460552936877105</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.3930117880916794</v>
+        <v>0.4011076660194483</v>
       </c>
     </row>
     <row r="112">
@@ -89981,13 +89981,13 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>1</v>
+        <v>0.03937322646379471</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.2460552936877103</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.393011861588663</v>
+        <v>0.4011077395164319</v>
       </c>
     </row>
     <row r="113">
@@ -90776,13 +90776,13 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>0</v>
+        <v>-0.05052801221609116</v>
       </c>
       <c r="JB113" t="n">
-        <v>0.3964372596156286</v>
+        <v>0.16</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.3930118983371549</v>
+        <v>0.4011077762649238</v>
       </c>
     </row>
     <row r="114">
@@ -91571,13 +91571,13 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>1</v>
+        <v>0.02885881252586842</v>
       </c>
       <c r="JB114" t="n">
-        <v>-0.2460552936877103</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.3930117880916794</v>
+        <v>0.4011076660194483</v>
       </c>
     </row>
     <row r="115">
@@ -92366,13 +92366,13 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>0</v>
+        <v>-0.03088924661278725</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.2460552936877103</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.3930122290735813</v>
+        <v>0.4011081070013502</v>
       </c>
     </row>
     <row r="116">
@@ -93161,13 +93161,13 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>0</v>
+        <v>-0.006362935528159142</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.8885478469910492</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.3930121188281057</v>
+        <v>0.4011079967558747</v>
       </c>
     </row>
     <row r="117">
@@ -93956,13 +93956,13 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>0</v>
+        <v>-0.02269373461604118</v>
       </c>
       <c r="JB117" t="n">
-        <v>-1.088547846991049</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.3930120820796138</v>
+        <v>0.4011079600073828</v>
       </c>
     </row>
     <row r="118">
@@ -94751,13 +94751,13 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>0</v>
+        <v>-0.02748292684555054</v>
       </c>
       <c r="JB118" t="n">
-        <v>-1.088547846991049</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.3930120085826302</v>
+        <v>0.4011078865103992</v>
       </c>
     </row>
     <row r="119">
@@ -95546,13 +95546,13 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>0</v>
+        <v>-0.03066534548997879</v>
       </c>
       <c r="JB119" t="n">
-        <v>-1.088547846991049</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.3930119718341385</v>
+        <v>0.4011078497619075</v>
       </c>
     </row>
     <row r="120">
@@ -96341,13 +96341,13 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>0</v>
+        <v>-0.02881994284689426</v>
       </c>
       <c r="JB120" t="n">
-        <v>-1.088547846991049</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.3930117513431874</v>
+        <v>0.4011076292709564</v>
       </c>
     </row>
     <row r="121">
@@ -97136,13 +97136,13 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>0</v>
+        <v>-0.001143837347626686</v>
       </c>
       <c r="JB121" t="n">
-        <v>-1.088547846991049</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.3930116778462038</v>
+        <v>0.4011075557739728</v>
       </c>
     </row>
     <row r="122">
@@ -97931,13 +97931,13 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>0</v>
+        <v>-0.02262787893414497</v>
       </c>
       <c r="JB122" t="n">
-        <v>-1.088547846991049</v>
+        <v>0.16</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.3930116043492202</v>
+        <v>0.4011074822769892</v>
       </c>
     </row>
     <row r="123">
@@ -98726,13 +98726,13 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>0</v>
+        <v>-0.01835921034216881</v>
       </c>
       <c r="JB123" t="n">
-        <v>-0.2460552936877103</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.3930116410977121</v>
+        <v>0.4011075190254811</v>
       </c>
     </row>
     <row r="124">
@@ -99521,13 +99521,13 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>1</v>
+        <v>0.001453803852200508</v>
       </c>
       <c r="JB124" t="n">
-        <v>0.3964372596156286</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.3930115308522366</v>
+        <v>0.4011074087800055</v>
       </c>
     </row>
     <row r="125">
@@ -100316,13 +100316,13 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>1</v>
+        <v>0.03278809040784836</v>
       </c>
       <c r="JB125" t="n">
-        <v>1.038929812918968</v>
+        <v>0.8600000000000005</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.3930116410977121</v>
+        <v>0.4011075190254811</v>
       </c>
     </row>
     <row r="126">
@@ -101111,13 +101111,13 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>1</v>
+        <v>0.008692404255270958</v>
       </c>
       <c r="JB126" t="n">
-        <v>1.038929812918968</v>
+        <v>1.280000000000001</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.3930119350856466</v>
+        <v>0.4011078130134155</v>
       </c>
     </row>
   </sheetData>
